--- a/Bump_Sensor_Test/XY_offset2.xlsx
+++ b/Bump_Sensor_Test/XY_offset2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c48cfaa2fe489af5/Documents/GitHub/SEMTM0042_43_Group/Bump_Sensor_Test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{0BEBD6A8-9799-4D36-A27C-E83D7B753A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA98E8EE-F9C9-469C-A274-760143F1F489}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{0BEBD6A8-9799-4D36-A27C-E83D7B753A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A02F6C2D-D14E-458C-9241-4B2941AE995D}"/>
   <bookViews>
-    <workbookView xWindow="15405" yWindow="-16320" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{38662949-59AC-423F-9A43-78756A473AC3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{38662949-59AC-423F-9A43-78756A473AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="x100_y0" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="x150_y0" sheetId="6" r:id="rId18"/>
     <sheet name="x150_y10" sheetId="11" r:id="rId19"/>
     <sheet name="x150_y-10" sheetId="12" r:id="rId20"/>
+    <sheet name="Sheet1" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30582,6 +30583,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{393B50BB-C495-4B02-9F64-F297407F12AA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B755A04D-5354-4087-83D0-2985EC081D3A}">
   <dimension ref="A1:I89"/>
